--- a/docs/tutorials/files/xslope_block_wall_grid.xlsx
+++ b/docs/tutorials/files/xslope_block_wall_grid.xlsx
@@ -3764,7 +3764,7 @@
         <v>0.6</v>
       </c>
       <c r="E3" s="3">
-        <v>12.2</v>
+        <v>14.2</v>
       </c>
       <c r="F3" s="3">
         <v>0.6</v>
@@ -3851,7 +3851,7 @@
         <v>1.8</v>
       </c>
       <c r="E4" s="3">
-        <v>12.2</v>
+        <v>14.2</v>
       </c>
       <c r="F4" s="3">
         <v>1.8</v>
@@ -3932,7 +3932,7 @@
         <v>3.0</v>
       </c>
       <c r="E5" s="3">
-        <v>12.2</v>
+        <v>14.2</v>
       </c>
       <c r="F5" s="3">
         <v>3.0</v>

--- a/docs/tutorials/files/xslope_block_wall_grid.xlsx
+++ b/docs/tutorials/files/xslope_block_wall_grid.xlsx
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <v>0.0</v>
+        <v>-0.2978258814</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>

--- a/docs/tutorials/files/xslope_block_wall_grid.xlsx
+++ b/docs/tutorials/files/xslope_block_wall_grid.xlsx
@@ -13757,20 +13757,10 @@
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
-        <v>10.6</v>
-      </c>
-      <c r="C3" s="3">
-        <v>11.2</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-      <c r="E3" s="3">
-        <v>-0.2978258814</v>
-      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>

--- a/docs/tutorials/files/xslope_block_wall_grid.xlsx
+++ b/docs/tutorials/files/xslope_block_wall_grid.xlsx
@@ -3776,11 +3776,11 @@
       </c>
       <c r="H3" s="3" t="str">
         <f>IF($G3="","",IFERROR(VLOOKUP($G3,$AH$8:$AJ$11,2,0),""))</f>
-        <v/>
+        <v>Tangent</v>
       </c>
       <c r="I3" s="3" t="str">
         <f t="shared" ref="I3:I32" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$AH$8:$AJ$11,3,0),""))</f>
-        <v/>
+        <v>Active</v>
       </c>
       <c r="J3" s="3">
         <v>40.0</v>
@@ -3863,11 +3863,11 @@
       </c>
       <c r="H4" s="3" t="str">
         <f>IF($G4="","",IFERROR(VLOOKUP($G4,$AH$8:$AJ$11,2,0),""))</f>
-        <v/>
+        <v>Tangent</v>
       </c>
       <c r="I4" s="3" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Active</v>
       </c>
       <c r="J4" s="3">
         <v>40.0</v>
@@ -3944,11 +3944,11 @@
       </c>
       <c r="H5" s="3" t="str">
         <f>IF($G5="","",IFERROR(VLOOKUP($G5,$AH$8:$AJ$11,2,0),""))</f>
-        <v/>
+        <v>Tangent</v>
       </c>
       <c r="I5" s="3" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Active</v>
       </c>
       <c r="J5" s="3">
         <v>40.0</v>
